--- a/LISTAS/mi/CORREDERA P CAJON.xlsx
+++ b/LISTAS/mi/CORREDERA P CAJON.xlsx
@@ -841,14 +841,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="14" t="n">
-        <v>45163.60862198231</v>
+        <v>45252</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -887,19 +883,6 @@
       </c>
       <c r="E10" s="9" t="n"/>
     </row>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
     <row r="24" ht="18" customHeight="1" s="1">
       <c r="A24" s="22" t="inlineStr">
         <is>
@@ -931,7 +914,7 @@
       </c>
       <c r="C25" s="27" t="n"/>
       <c r="D25" s="12" t="n">
-        <v>553.023</v>
+        <v>635.976</v>
       </c>
     </row>
     <row r="26" ht="19.5" customHeight="1" s="1">
@@ -947,7 +930,7 @@
       </c>
       <c r="C26" s="25" t="n"/>
       <c r="D26" s="12" t="n">
-        <v>616.63</v>
+        <v>709.125</v>
       </c>
     </row>
     <row r="27" ht="19.5" customHeight="1" s="1">
@@ -963,7 +946,7 @@
       </c>
       <c r="C27" s="27" t="n"/>
       <c r="D27" s="12" t="n">
-        <v>694.963</v>
+        <v>799.207</v>
       </c>
     </row>
     <row r="28" ht="19.5" customHeight="1" s="1">
@@ -979,7 +962,7 @@
       </c>
       <c r="C28" s="27" t="n"/>
       <c r="D28" s="13" t="n">
-        <v>760.926</v>
+        <v>875.0650000000001</v>
       </c>
     </row>
     <row r="29" ht="19.5" customHeight="1" s="1">
@@ -995,7 +978,7 @@
       </c>
       <c r="C29" s="27" t="n"/>
       <c r="D29" s="12" t="n">
-        <v>836.306</v>
+        <v>961.752</v>
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1" s="1">
@@ -1011,11 +994,9 @@
       </c>
       <c r="C30" s="25" t="n"/>
       <c r="D30" s="13" t="n">
-        <v>912.873</v>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="32"/>
+        <v>1049.804</v>
+      </c>
+    </row>
     <row r="33" ht="19.5" customHeight="1" s="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
@@ -1025,16 +1006,16 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B28:C28"/>
     <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B26:C26"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
     <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>

--- a/LISTAS/mi/CORREDERA P CAJON.xlsx
+++ b/LISTAS/mi/CORREDERA P CAJON.xlsx
@@ -841,7 +841,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="14" t="n">
-        <v>45252</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
@@ -1006,17 +1006,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B25:C25"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B24:C24"/>
     <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/CORREDERA P CAJON.xlsx
+++ b/LISTAS/mi/CORREDERA P CAJON.xlsx
@@ -841,7 +841,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="14" t="n">
-        <v>45253</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
@@ -1006,17 +1006,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B25:C25"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B24:C24"/>
     <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/CORREDERA P CAJON.xlsx
+++ b/LISTAS/mi/CORREDERA P CAJON.xlsx
@@ -841,7 +841,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="14" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/mi/CORREDERA P CAJON.xlsx
+++ b/LISTAS/mi/CORREDERA P CAJON.xlsx
@@ -841,10 +841,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="14" t="n">
-        <v>45266</v>
+        <v>45261.57771112799</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -883,6 +887,19 @@
       </c>
       <c r="E10" s="9" t="n"/>
     </row>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
     <row r="24" ht="18" customHeight="1" s="1">
       <c r="A24" s="22" t="inlineStr">
         <is>
@@ -914,7 +931,7 @@
       </c>
       <c r="C25" s="27" t="n"/>
       <c r="D25" s="12" t="n">
-        <v>635.976</v>
+        <v>973.45</v>
       </c>
     </row>
     <row r="26" ht="19.5" customHeight="1" s="1">
@@ -930,7 +947,7 @@
       </c>
       <c r="C26" s="25" t="n"/>
       <c r="D26" s="12" t="n">
-        <v>709.125</v>
+        <v>1085.42</v>
       </c>
     </row>
     <row r="27" ht="19.5" customHeight="1" s="1">
@@ -946,7 +963,7 @@
       </c>
       <c r="C27" s="27" t="n"/>
       <c r="D27" s="12" t="n">
-        <v>799.207</v>
+        <v>1223.3</v>
       </c>
     </row>
     <row r="28" ht="19.5" customHeight="1" s="1">
@@ -962,7 +979,7 @@
       </c>
       <c r="C28" s="27" t="n"/>
       <c r="D28" s="13" t="n">
-        <v>875.0650000000001</v>
+        <v>1339.41</v>
       </c>
     </row>
     <row r="29" ht="19.5" customHeight="1" s="1">
@@ -978,7 +995,7 @@
       </c>
       <c r="C29" s="27" t="n"/>
       <c r="D29" s="12" t="n">
-        <v>961.752</v>
+        <v>1472.1</v>
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1" s="1">
@@ -994,9 +1011,11 @@
       </c>
       <c r="C30" s="25" t="n"/>
       <c r="D30" s="13" t="n">
-        <v>1049.804</v>
-      </c>
-    </row>
+        <v>1606.88</v>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32"/>
     <row r="33" ht="19.5" customHeight="1" s="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
@@ -1006,16 +1025,16 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B25:C25"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
     <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>

--- a/LISTAS/mi/CORREDERA P CAJON.xlsx
+++ b/LISTAS/mi/CORREDERA P CAJON.xlsx
@@ -841,14 +841,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="14" t="n">
-        <v>45261.57771112799</v>
+        <v>45286</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -887,19 +883,6 @@
       </c>
       <c r="E10" s="9" t="n"/>
     </row>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
     <row r="24" ht="18" customHeight="1" s="1">
       <c r="A24" s="22" t="inlineStr">
         <is>
@@ -931,7 +914,7 @@
       </c>
       <c r="C25" s="27" t="n"/>
       <c r="D25" s="12" t="n">
-        <v>973.45</v>
+        <v>635.976</v>
       </c>
     </row>
     <row r="26" ht="19.5" customHeight="1" s="1">
@@ -947,7 +930,7 @@
       </c>
       <c r="C26" s="25" t="n"/>
       <c r="D26" s="12" t="n">
-        <v>1085.42</v>
+        <v>709.125</v>
       </c>
     </row>
     <row r="27" ht="19.5" customHeight="1" s="1">
@@ -963,7 +946,7 @@
       </c>
       <c r="C27" s="27" t="n"/>
       <c r="D27" s="12" t="n">
-        <v>1223.3</v>
+        <v>799.207</v>
       </c>
     </row>
     <row r="28" ht="19.5" customHeight="1" s="1">
@@ -979,7 +962,7 @@
       </c>
       <c r="C28" s="27" t="n"/>
       <c r="D28" s="13" t="n">
-        <v>1339.41</v>
+        <v>875.0650000000001</v>
       </c>
     </row>
     <row r="29" ht="19.5" customHeight="1" s="1">
@@ -995,7 +978,7 @@
       </c>
       <c r="C29" s="27" t="n"/>
       <c r="D29" s="12" t="n">
-        <v>1472.1</v>
+        <v>961.752</v>
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1" s="1">
@@ -1011,11 +994,9 @@
       </c>
       <c r="C30" s="25" t="n"/>
       <c r="D30" s="13" t="n">
-        <v>1606.88</v>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="32"/>
+        <v>1049.804</v>
+      </c>
+    </row>
     <row r="33" ht="19.5" customHeight="1" s="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
@@ -1025,17 +1006,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B27:C27"/>
     <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>
